--- a/web/e2e/fixtures/import.xlsx
+++ b/web/e2e/fixtures/import.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,19 +414,10 @@
         <v>量化指标</v>
       </c>
       <c r="E1" t="str">
-        <v>任务名称</v>
+        <v>周期开始</v>
       </c>
       <c r="F1" t="str">
-        <v>任务负责人</v>
-      </c>
-      <c r="G1" t="str">
-        <v>开始</v>
-      </c>
-      <c r="H1" t="str">
-        <v>截止</v>
-      </c>
-      <c r="I1" t="str">
-        <v>预期交付物</v>
+        <v>周期截止</v>
       </c>
     </row>
     <row r="2">
@@ -442,20 +433,11 @@
       <c r="D2" t="str">
         <v>不兼容对象 100% 登记</v>
       </c>
-      <c r="E2" t="str">
-        <v>盘点对象、清单，含不兼容项</v>
-      </c>
-      <c r="F2" t="str">
-        <v>陈牧阳</v>
-      </c>
-      <c r="G2" s="1">
+      <c r="E2" s="1">
         <v>46090</v>
       </c>
-      <c r="H2" s="1">
-        <v>46107</v>
-      </c>
-      <c r="I2" t="str">
-        <v>不兼容对象清单</v>
+      <c r="F2" s="1">
+        <v>46165</v>
       </c>
     </row>
     <row r="3">
@@ -463,28 +445,19 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>应用侧 SQL 与驱动完成适配</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>王浩然</v>
       </c>
       <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>输出改造清单与工作量评估</v>
-      </c>
-      <c r="F3" t="str">
-        <v>王浩然</v>
-      </c>
-      <c r="G3" s="1">
-        <v>46097</v>
-      </c>
-      <c r="H3" s="1">
+        <v>回归用例通过率 ≥ 99%</v>
+      </c>
+      <c r="E3" s="1">
         <v>46115</v>
       </c>
-      <c r="I3" t="str">
-        <v>存储过程改造清单</v>
+      <c r="F3" s="1">
+        <v>46245</v>
       </c>
     </row>
     <row r="4">
@@ -506,19 +479,10 @@
       <c r="F4" t="str">
         <v/>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>